--- a/AAII_Financials/Yearly/IBN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IBN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
   <si>
     <t>IBN</t>
   </si>
@@ -656,124 +656,130 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42460</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>21123400</v>
+      </c>
+      <c r="E8" s="3">
         <v>21325400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>17137800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14235400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13036700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13189100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10965300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10343800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10255000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7306700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7168600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7101300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6798400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5933700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5494100</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -819,39 +825,42 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>21123400</v>
+      </c>
+      <c r="E10" s="3">
         <v>21325400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>17137800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>14235400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13036700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>13189100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10965300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10343800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10255000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -867,9 +876,12 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,8 +900,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -935,9 +948,12 @@
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,9 +999,12 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1013,8 +1032,8 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1031,57 +1050,63 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>314900</v>
+        <v>320800</v>
       </c>
       <c r="E15" s="3">
+        <v>304900</v>
+      </c>
+      <c r="F15" s="3">
         <v>239500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>199100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>193700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>201100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>181900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>150900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>159700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-109300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-101900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-103100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-98800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-82700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-97100</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14972700</v>
+      </c>
+      <c r="E17" s="3">
         <v>14956700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11736000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10038800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9639200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10425300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9497800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9274600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8567900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6064700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5043400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4644600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4423200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3944400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3768900</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6150700</v>
+      </c>
+      <c r="E18" s="3">
         <v>6368700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5401800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4196600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3397500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2763800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1467500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1069200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1687000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1242000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2125200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2456700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2375200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1989300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1725200</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,89 +1245,93 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-17600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-128900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-121600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-99400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-19700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-23300</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>413700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-395800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-88000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-138100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-189200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-179900</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6701200</v>
+        <v>6499600</v>
       </c>
       <c r="E21" s="3">
+        <v>6691300</v>
+      </c>
+      <c r="F21" s="3">
         <v>5770200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4517300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3690600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2984600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1672700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1220100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1846700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1780700</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1305,12 +1341,15 @@
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>1654500</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1338,8 +1377,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1356,57 +1395,63 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6178800</v>
+      </c>
+      <c r="E23" s="3">
         <v>6386400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5530600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4318200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3496900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2783500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1490800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1069200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1687000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1655700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1729400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2368700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2237100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1800100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1545300</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1428,33 +1473,36 @@
       <c r="I24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
         <v>248100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>288700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>296000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>408300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>696600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>633300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>461000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>397500</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6178800</v>
+      </c>
+      <c r="E26" s="3">
         <v>6386400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5530600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4318200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3496900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2783500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1490800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>821100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1398300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1359700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1321100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1672100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1603700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1339200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1147800</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5781100</v>
+      </c>
+      <c r="E27" s="3">
         <v>5972100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5311700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4144700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3308800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2512900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1270400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>614000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1185100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1221600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1230800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1582300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1516400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1335900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1023900</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1674,8 +1734,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>5</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>5</v>
@@ -1686,15 +1746,18 @@
       <c r="O29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,105 +1854,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E32" s="3">
         <v>17600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>128900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>121600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>99400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>19700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>23300</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>-413700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>395800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>88000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>138100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>189200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>179900</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5781100</v>
+      </c>
+      <c r="E33" s="3">
         <v>5972000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5311700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4144700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3308800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2512900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1270400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>614000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1185100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1221600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1230800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1582300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1516400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1335900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1023900</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5781100</v>
+      </c>
+      <c r="E35" s="3">
         <v>5972000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5311700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4144700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3308800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2512900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1270400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>614000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1185100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1221600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1230800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1582300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1516400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1335900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1023900</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42460</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,74 +2159,78 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15921700</v>
+      </c>
+      <c r="E41" s="3">
         <v>11735500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9815500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9314200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10636800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14818200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13613700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8405300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9825300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6957800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6136300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5980200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5999100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2554200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2997300</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2300700</v>
+      </c>
+      <c r="E42" s="3">
         <v>1891800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2040200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2167800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1388200</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -2152,26 +2241,29 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>27788600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>18542900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>22171000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>22326800</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2196,12 +2288,12 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L43" s="3">
         <v>61300</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -2217,9 +2309,12 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2241,15 +2336,15 @@
       <c r="I44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K44" s="3">
         <v>144900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>303500</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
@@ -2265,39 +2360,42 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4133400</v>
+        <v>4116000</v>
       </c>
       <c r="E45" s="3">
+        <v>4136600</v>
+      </c>
+      <c r="F45" s="3">
         <v>3526600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2756500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2302400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2582000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2882300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3134000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2673500</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2313,39 +2411,42 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>31072800</v>
+        <v>34676300</v>
       </c>
       <c r="E46" s="3">
+        <v>31076000</v>
+      </c>
+      <c r="F46" s="3">
         <v>25102600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>21540900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>27821100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22752900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19861500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15892100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16714600</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2361,45 +2462,48 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>76753400</v>
+      </c>
+      <c r="E47" s="3">
         <v>84864200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>79492500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>60337200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>54846800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>54405300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>46001100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>41459900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>42213700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>45100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>44700</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
@@ -2409,105 +2513,114 @@
       <c r="Q47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1857800</v>
+      </c>
+      <c r="E48" s="3">
         <v>1850600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1589100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1335700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1397500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1477500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1382300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1394300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1454500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1119600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1053500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>758600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>756600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>724100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>785500</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1125100</v>
+      </c>
+      <c r="E49" s="3">
         <v>990000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>297000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>15800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>17200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15200</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>19700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>18900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>20700</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,57 +2717,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>23619600</v>
+        <v>20558500</v>
       </c>
       <c r="E52" s="3">
+        <v>23616300</v>
+      </c>
+      <c r="F52" s="3">
         <v>25179200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>22350600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>24549900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>26964000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>20687500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25079200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>24057700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1346000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>599800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>208500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>127800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>354600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>405400</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>310825000</v>
+      </c>
+      <c r="E54" s="3">
         <v>309226900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>283737700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>238489000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>230945100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>215118900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>182907800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>178796800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>172767000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>118188000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>111078000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>106729000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>102743000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>89278900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>89548900</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,86 +2915,90 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>202131800</v>
+      </c>
+      <c r="E57" s="3">
         <v>199371500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>180931000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>150402200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>146530400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>136243400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>111000800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>103198700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>94311000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3179300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2412900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2288200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2637600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2609300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2105500</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>16917600</v>
+        <v>5309300</v>
       </c>
       <c r="E58" s="3">
-        <v>14551100</v>
+        <v>4824900</v>
       </c>
       <c r="F58" s="3">
+        <v>16669700</v>
+      </c>
+      <c r="G58" s="3">
         <v>12577700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1192900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>578600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>430700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>275600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>198300</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -2881,87 +3014,93 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1053800</v>
+      </c>
+      <c r="E59" s="3">
         <v>1059300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1543600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1695900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1780300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1800800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>857700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1256200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1143700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>397300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>422500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>407000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>349000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>311500</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>217841800</v>
+        <v>208943300</v>
       </c>
       <c r="E60" s="3">
-        <v>197493700</v>
+        <v>205749100</v>
       </c>
       <c r="F60" s="3">
+        <v>199612300</v>
+      </c>
+      <c r="G60" s="3">
         <v>165082400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>149866300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>138962100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>112697000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>105259500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>96204600</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2977,105 +3116,114 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10888200</v>
+        <v>20894800</v>
       </c>
       <c r="E61" s="3">
-        <v>12469600</v>
+        <v>22980800</v>
       </c>
       <c r="F61" s="3">
+        <v>10351000</v>
+      </c>
+      <c r="G61" s="3">
         <v>12691300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>21601200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>19102800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>27973700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>30080800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>35053700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>22430800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>26538500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>27293800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>25218700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>22873100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>23323500</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>40506400</v>
+      </c>
+      <c r="E62" s="3">
         <v>42023500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>41364900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>33781200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>34700400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>34203300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>25005400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26016500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>23585100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>306000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>352800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>329600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>294600</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>270344500</v>
+      </c>
+      <c r="E66" s="3">
         <v>270753400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>251328100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>211554900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>206167900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>192268200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>165676100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>161356700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>154843400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>105643000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>99699600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>95785600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>92241100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>80181600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>80688300</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>28949200</v>
+      </c>
+      <c r="E72" s="3">
         <v>26434600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>21622800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>17217300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>14606300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>12156700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9235900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8927700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9047000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7922300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6759100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6373200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5639000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4568300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4003000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>38719600</v>
+      </c>
+      <c r="E76" s="3">
         <v>36737000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>30742700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>26119800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23989100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21540100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16329400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16490400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17000300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12545400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11378000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10943800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10501500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9097300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8860600</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42460</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5781100</v>
+      </c>
+      <c r="E81" s="3">
         <v>5972000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5311700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4144700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3308800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2512900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1270400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>614000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1185100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1221600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1230800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1582300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1516400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1335900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1023900</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,41 +4084,42 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>314900</v>
+        <v>320800</v>
       </c>
       <c r="E83" s="3">
+        <v>304900</v>
+      </c>
+      <c r="F83" s="3">
         <v>239500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>199100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>193700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>201100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>181900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>150900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>159700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>125200</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
@@ -3931,12 +4129,15 @@
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>109100</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-12910200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8806900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-9086600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-15006900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9660600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2889600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5299200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6761900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8271400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6311000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1483800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>874000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>929500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2312700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-985300</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-397800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-558200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-441500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-245100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-230800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-248800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-165700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-160100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-157900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-150500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-108200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-115100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-82600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-87500</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,42 +4612,45 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1387900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9045200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17514800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8281100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5181400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8609500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5618700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4351200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7771600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-192500</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
@@ -4431,12 +4660,15 @@
       <c r="P94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>-3074600</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,26 +4687,27 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>837500</v>
+      </c>
+      <c r="E96" s="3">
         <v>824100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>672000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>423700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>182500</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -4485,26 +4718,29 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-410400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-372900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-349400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-371500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-293400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-274900</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,42 +4888,45 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>19593300</v>
+      </c>
+      <c r="E100" s="3">
         <v>23833200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>29616100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>17566400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>19617500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>14282200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>16263000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>10900400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>17346900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4252800</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
@@ -4691,45 +4936,48 @@
       <c r="P100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>4256900</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>139300</v>
+      </c>
+      <c r="E101" s="3">
         <v>17400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>50800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>38500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-16700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-88000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>28400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-19400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-12600</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
@@ -4739,58 +4987,64 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
         <v>59100</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5434500</v>
+      </c>
+      <c r="E102" s="3">
         <v>5998400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3065500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5683000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4758800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2695100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5373500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-232100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1307500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1853000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-75100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-143800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-152900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1086000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>256100</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
